--- a/Result/profitability/2915.xlsx
+++ b/Result/profitability/2915.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>2.1175</v>
+        <v>2.51125</v>
       </c>
       <c r="N2" t="n">
-        <v>39.87875</v>
+        <v>42.0775</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.76</v>
+        <v>2.31875</v>
       </c>
       <c r="N3" t="n">
-        <v>40.88</v>
+        <v>40.9125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5075</v>
+        <v>2.5175</v>
       </c>
       <c r="N4" t="n">
-        <v>36.55875</v>
+        <v>38.63875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7625</v>
+        <v>4.09</v>
       </c>
       <c r="N5" t="n">
-        <v>36.61499999999999</v>
+        <v>38.18875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0275</v>
+        <v>1.485</v>
       </c>
       <c r="N6" t="n">
-        <v>34.035</v>
+        <v>34.35375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.68</v>
       </c>
       <c r="M7" t="n">
-        <v>0.775</v>
+        <v>1.2475</v>
       </c>
       <c r="N7" t="n">
-        <v>33.59</v>
+        <v>32.46375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.44</v>
+        <v>0.91125</v>
       </c>
       <c r="N8" t="n">
-        <v>28.18875</v>
+        <v>28.7625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9356,25 +9356,25 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6052</v>
+        <v>-12741</v>
       </c>
       <c r="J71" t="n">
-        <v>6082</v>
+        <v>-12711</v>
       </c>
       <c r="K71" t="n">
-        <v>5992</v>
+        <v>-12801</v>
       </c>
       <c r="L71" t="n">
-        <v>5.74</v>
+        <v>-12.27</v>
       </c>
       <c r="M71" t="n">
-        <v>2.46625</v>
+        <v>0.2150000000000001</v>
       </c>
       <c r="N71" t="n">
         <v>36.865</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -9386,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
@@ -9398,10 +9398,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>7.470000000000001</v>
+        <v>-10.54</v>
       </c>
       <c r="X71" t="n">
-        <v>-4.317919075144509</v>
+        <v>6.092485549132948</v>
       </c>
       <c r="Y71" t="n">
         <v>4.050000000000004</v>
@@ -9410,10 +9410,10 @@
         <v>0.1240428790199082</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.1</v>
+        <v>-15.91</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.5769230769230769</v>
+        <v>-4.37087912087912</v>
       </c>
       <c r="AC71" t="n">
         <v>-1.299999999999997</v>
@@ -9422,10 +9422,10 @@
         <v>-0.03421052631578936</v>
       </c>
       <c r="AE71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>1</v>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>EPS成長 / 毛利率衰退</t>
+          <t>EPS衰退 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK71" t="n">
@@ -9483,19 +9483,19 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2857</v>
+        <v>21650</v>
       </c>
       <c r="J72" t="n">
-        <v>2964</v>
+        <v>21757</v>
       </c>
       <c r="K72" t="n">
-        <v>2813</v>
+        <v>21606</v>
       </c>
       <c r="L72" t="n">
-        <v>2.7</v>
+        <v>20.7</v>
       </c>
       <c r="M72" t="n">
-        <v>2.01875</v>
+        <v>2.0175</v>
       </c>
       <c r="N72" t="n">
         <v>38.27875</v>
@@ -9507,7 +9507,7 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -9525,10 +9525,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>-3.04</v>
+        <v>32.97</v>
       </c>
       <c r="X72" t="n">
-        <v>-0.5296167247386759</v>
+        <v>-2.687041564792176</v>
       </c>
       <c r="Y72" t="n">
         <v>10.04</v>
@@ -9537,10 +9537,10 @@
         <v>0.2735694822888284</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.15625</v>
+        <v>5.468749999999999</v>
       </c>
       <c r="AC72" t="n">
         <v>15.04</v>
@@ -9549,10 +9549,10 @@
         <v>0.4744479495268139</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG72" t="n">
         <v>1</v>
@@ -9561,11 +9561,11 @@
         <v>1</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>EPS衰退 / 毛利率成長</t>
+          <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
       <c r="AK72" t="n">
@@ -9622,7 +9622,7 @@
         <v>2.58</v>
       </c>
       <c r="M73" t="n">
-        <v>2.78625</v>
+        <v>2.785</v>
       </c>
       <c r="N73" t="n">
         <v>40.5475</v>
@@ -9652,10 +9652,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>-0.1200000000000001</v>
+        <v>-18.12</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.04444444444444451</v>
+        <v>-0.8753623188405797</v>
       </c>
       <c r="Y73" t="n">
         <v>11.56</v>
@@ -9749,7 +9749,7 @@
         <v>2.59</v>
       </c>
       <c r="M74" t="n">
-        <v>2.575</v>
+        <v>2.57375</v>
       </c>
       <c r="N74" t="n">
         <v>42.2275</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2915</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>567</v>
+      </c>
+      <c r="D75" t="n">
+        <v>288</v>
+      </c>
+      <c r="E75" t="n">
+        <v>280</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>76</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.32%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6689</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6764</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6641</v>
+      </c>
+      <c r="L75" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.91375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.63875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.455598455598456</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.589999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1026845637583891</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.518337408312958</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3430517711171661</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
